--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0115.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0115.xlsx
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nói đơn giản, chúng ta "chế tạo vũ khí". Cụ thể hơn là Broadblade, Kiếm... toàn bộ kho vũ khí cổ điển ấy.</t>
+          <t>Nói đơn giản, chúng ta "chế tạo vũ khí". Cụ thể hơn là Đại kiếm, Kiếm... toàn bộ kho vũ khí cổ điển ấy.</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Ta đã xử lý xong rồi.</t>
+          <t>Tao đã xử lý xong rồi.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tốt rồi. Ta định gửi cho ngươi tấm ảnh. Nhưng...</t>
+          <t>Tốt rồi. Tao định gửi cho mày tấm ảnh. Nhưng...</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Bạn đang nhìn gì vậy?</t>
+          <t>Nhìn gì thế?</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Ta sẽ đánh dấu ba tấm đá khắc còn lại lên bản đồ của ngươi.</t>
+          <t>Tao sẽ đánh dấu ba tấm đá khắc còn lại lên bản đồ của mày.</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Lại sáng rồi à? Ồ... Lâu lắm rồi ta không thấy chúng sáng thế này. Đẹp thật đấy, nhất là vào ban đêm.</t>
+          <t>Lại sáng rồi à? Ồ... Lâu lắm rồi tao không thấy chúng sáng thế này. Đẹp thật đấy, nhất là vào ban đêm.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Ta sẽ đánh dấu ba tấm đá khắc còn lại lên bản đồ của ngươi.</t>
+          <t>Tao sẽ đánh dấu ba tấm đá khắc còn lại lên bản đồ của mày.</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Ta không biết cậu đã thấy cái Zip Zap này chưa, nhưng nó giúp ích nhiều lắm đấy.</t>
+          <t>Tao không biết cậu đã thấy cái Zip Zap này chưa, nhưng nó giúp ích nhiều lắm đấy.</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Bạn đang nhìn gì vậy?</t>
+          <t>Nhìn gì thế?</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Ta muốn thắp sáng lại những bức tường này để chúng không bị lãng quên trong bóng tối.</t>
+          <t>Tao muốn thắp sáng lại những bức tường này để chúng không bị lãng quên trong bóng tối.</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Cứ gọi ta là {PlayerName} đi.</t>
+          <t>Cứ gọi tao là {PlayerName} đi.</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tch, bọn bay đúng là vô vọng. Làm gì ta lại sợ chứ.</t>
+          <t>Tch, bọn bay đúng là vô vọng. Làm gì tao lại sợ chứ.</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Tránh ra! TRÁNH XA Ta ĐI!</t>
+          <t>Tránh ra! TRÁNH XA TAO ĐI!</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Ta nói rồi mà. Câu lạc bộ Siêu nhiên của chúng ta đâu phải nhóm sở thích vớ vẩn. Khi có chuyện kỳ lạ xảy ra, tụi mình là những người biết đầu tiên.</t>
+          <t>Tao nói rồi mà. Câu lạc bộ Siêu nhiên của chúng ta đâu phải nhóm sở thích vớ vẩn. Khi có chuyện kỳ lạ xảy ra, tụi mình là những người biết đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Ừ thì, ta biết chuyện của cô ta. Và tin ta đi, phe Hắc Ám có những bí mật nặng ký hơn thế nhiều.</t>
+          <t>Ừ thì, tao biết chuyện của cô ta. Và tin tao đi, phe Hắc Ám có những bí mật nặng ký hơn thế nhiều.</t>
         </is>
       </c>
     </row>
